--- a/AAII_Financials/Yearly/CMAKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CMAKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>CMAKY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -688,19 +688,19 @@
         <v>45657</v>
       </c>
       <c r="F7" s="2">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G7" s="2">
-        <v>44926</v>
+        <v>44561</v>
       </c>
       <c r="H7" s="2">
-        <v>44561</v>
+        <v>44196</v>
       </c>
       <c r="I7" s="2">
-        <v>44196</v>
+        <v>43830</v>
       </c>
       <c r="J7" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K7" s="2">
         <v>43465</v>
@@ -715,25 +715,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>12256500</v>
+        <v>12649800</v>
       </c>
       <c r="E8" s="3">
-        <v>12008200</v>
+        <v>12379300</v>
       </c>
       <c r="F8" s="3">
-        <v>13295500</v>
+        <v>13478200</v>
       </c>
       <c r="G8" s="3">
-        <v>13478200</v>
+        <v>14239500</v>
       </c>
       <c r="H8" s="3">
-        <v>14239500</v>
+        <v>14009300</v>
       </c>
       <c r="I8" s="3">
-        <v>14009300</v>
+        <v>16894400</v>
       </c>
       <c r="J8" s="3">
-        <v>16894400</v>
+        <v>15686500</v>
       </c>
       <c r="K8" s="3">
         <v>15686500</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>12256500</v>
+        <v>12649800</v>
       </c>
       <c r="E10" s="3">
-        <v>12008200</v>
+        <v>12379300</v>
       </c>
       <c r="F10" s="3">
-        <v>13295500</v>
+        <v>13478200</v>
       </c>
       <c r="G10" s="3">
-        <v>13478200</v>
+        <v>14239500</v>
       </c>
       <c r="H10" s="3">
-        <v>14239500</v>
+        <v>14009300</v>
       </c>
       <c r="I10" s="3">
-        <v>14009300</v>
+        <v>16894400</v>
       </c>
       <c r="J10" s="3">
-        <v>16894400</v>
+        <v>15686500</v>
       </c>
       <c r="K10" s="3">
         <v>15686500</v>
@@ -894,11 +894,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-62700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -906,11 +906,11 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
         <v>-76900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>835800</v>
+        <v>613800</v>
       </c>
       <c r="E15" s="3">
-        <v>774500</v>
+        <v>611400</v>
       </c>
       <c r="F15" s="3">
-        <v>745900</v>
+        <v>669000</v>
       </c>
       <c r="G15" s="3">
-        <v>669000</v>
+        <v>644600</v>
       </c>
       <c r="H15" s="3">
-        <v>644600</v>
+        <v>571300</v>
       </c>
       <c r="I15" s="3">
-        <v>571300</v>
+        <v>444800</v>
       </c>
       <c r="J15" s="3">
-        <v>444800</v>
+        <v>1046400</v>
       </c>
       <c r="K15" s="3">
         <v>1046400</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7644400</v>
+        <v>8016700</v>
       </c>
       <c r="E17" s="3">
-        <v>7338400</v>
+        <v>7736800</v>
       </c>
       <c r="F17" s="3">
-        <v>8027000</v>
+        <v>8089100</v>
       </c>
       <c r="G17" s="3">
-        <v>8089100</v>
+        <v>8635500</v>
       </c>
       <c r="H17" s="3">
-        <v>8635500</v>
+        <v>8389500</v>
       </c>
       <c r="I17" s="3">
-        <v>8389500</v>
+        <v>7569000</v>
       </c>
       <c r="J17" s="3">
-        <v>7569000</v>
+        <v>7139300</v>
       </c>
       <c r="K17" s="3">
         <v>7139300</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4612100</v>
+        <v>4633100</v>
       </c>
       <c r="E18" s="3">
-        <v>4669800</v>
+        <v>4642500</v>
       </c>
       <c r="F18" s="3">
-        <v>5268400</v>
+        <v>5389100</v>
       </c>
       <c r="G18" s="3">
-        <v>5389100</v>
+        <v>5604000</v>
       </c>
       <c r="H18" s="3">
-        <v>5604000</v>
+        <v>5619700</v>
       </c>
       <c r="I18" s="3">
-        <v>5619700</v>
+        <v>9325400</v>
       </c>
       <c r="J18" s="3">
-        <v>9325400</v>
+        <v>8547200</v>
       </c>
       <c r="K18" s="3">
         <v>8547200</v>
@@ -1053,11 +1053,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>35500</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
@@ -1065,14 +1065,14 @@
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
+      <c r="H20" s="3">
+        <v>74300</v>
       </c>
       <c r="I20" s="3">
-        <v>74300</v>
-      </c>
-      <c r="J20" s="3">
         <v>27900</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5447900</v>
+        <v>5163400</v>
       </c>
       <c r="E21" s="3">
-        <v>5444200</v>
+        <v>5218500</v>
       </c>
       <c r="F21" s="3">
-        <v>6014300</v>
+        <v>6058100</v>
       </c>
       <c r="G21" s="3">
-        <v>6058100</v>
+        <v>6248600</v>
       </c>
       <c r="H21" s="3">
-        <v>6248600</v>
+        <v>6116800</v>
       </c>
       <c r="I21" s="3">
-        <v>6116800</v>
+        <v>9742300</v>
       </c>
       <c r="J21" s="3">
-        <v>9742300</v>
+        <v>9593600</v>
       </c>
       <c r="K21" s="3">
         <v>9593600</v>
@@ -1159,19 +1159,19 @@
         <v>4669800</v>
       </c>
       <c r="F23" s="3">
-        <v>5268400</v>
+        <v>5389100</v>
       </c>
       <c r="G23" s="3">
-        <v>5389100</v>
+        <v>5604000</v>
       </c>
       <c r="H23" s="3">
-        <v>5604000</v>
+        <v>5622300</v>
       </c>
       <c r="I23" s="3">
-        <v>5622300</v>
+        <v>9297600</v>
       </c>
       <c r="J23" s="3">
-        <v>9297600</v>
+        <v>8547200</v>
       </c>
       <c r="K23" s="3">
         <v>8547200</v>
@@ -1192,19 +1192,19 @@
         <v>186700</v>
       </c>
       <c r="F24" s="3">
-        <v>193500</v>
+        <v>202000</v>
       </c>
       <c r="G24" s="3">
-        <v>202000</v>
+        <v>117600</v>
       </c>
       <c r="H24" s="3">
-        <v>117600</v>
+        <v>245700</v>
       </c>
       <c r="I24" s="3">
-        <v>245700</v>
+        <v>1409500</v>
       </c>
       <c r="J24" s="3">
-        <v>1409500</v>
+        <v>1229300</v>
       </c>
       <c r="K24" s="3">
         <v>1229300</v>
@@ -1258,19 +1258,19 @@
         <v>4483000</v>
       </c>
       <c r="F26" s="3">
-        <v>5075000</v>
+        <v>5187200</v>
       </c>
       <c r="G26" s="3">
-        <v>5187200</v>
+        <v>5486400</v>
       </c>
       <c r="H26" s="3">
-        <v>5486400</v>
+        <v>5376700</v>
       </c>
       <c r="I26" s="3">
-        <v>5376700</v>
+        <v>7888100</v>
       </c>
       <c r="J26" s="3">
-        <v>7888100</v>
+        <v>7317900</v>
       </c>
       <c r="K26" s="3">
         <v>7317900</v>
@@ -1291,19 +1291,19 @@
         <v>3833300</v>
       </c>
       <c r="F27" s="3">
-        <v>4443300</v>
+        <v>4518200</v>
       </c>
       <c r="G27" s="3">
-        <v>4518200</v>
+        <v>4888200</v>
       </c>
       <c r="H27" s="3">
-        <v>4888200</v>
+        <v>4744100</v>
       </c>
       <c r="I27" s="3">
-        <v>4744100</v>
+        <v>7649300</v>
       </c>
       <c r="J27" s="3">
-        <v>7649300</v>
+        <v>7237400</v>
       </c>
       <c r="K27" s="3">
         <v>7237400</v>
@@ -1449,11 +1449,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-35500</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
@@ -1461,14 +1461,14 @@
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
+      <c r="H32" s="3">
+        <v>-74300</v>
       </c>
       <c r="I32" s="3">
-        <v>-74300</v>
-      </c>
-      <c r="J32" s="3">
         <v>-27900</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -1489,19 +1489,19 @@
         <v>4424700</v>
       </c>
       <c r="F33" s="3">
-        <v>5052000</v>
+        <v>5113500</v>
       </c>
       <c r="G33" s="3">
-        <v>5113500</v>
+        <v>5412100</v>
       </c>
       <c r="H33" s="3">
-        <v>5412100</v>
+        <v>5255200</v>
       </c>
       <c r="I33" s="3">
-        <v>5255200</v>
+        <v>7729400</v>
       </c>
       <c r="J33" s="3">
-        <v>7729400</v>
+        <v>7317400</v>
       </c>
       <c r="K33" s="3">
         <v>7317400</v>
@@ -1555,19 +1555,19 @@
         <v>4424700</v>
       </c>
       <c r="F35" s="3">
-        <v>5052000</v>
+        <v>5113500</v>
       </c>
       <c r="G35" s="3">
-        <v>5113500</v>
+        <v>5412100</v>
       </c>
       <c r="H35" s="3">
-        <v>5412100</v>
+        <v>5255200</v>
       </c>
       <c r="I35" s="3">
-        <v>5255200</v>
+        <v>7729400</v>
       </c>
       <c r="J35" s="3">
-        <v>7729400</v>
+        <v>7317400</v>
       </c>
       <c r="K35" s="3">
         <v>7317400</v>
@@ -1593,19 +1593,19 @@
         <v>45657</v>
       </c>
       <c r="F38" s="2">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G38" s="2">
-        <v>44926</v>
+        <v>44561</v>
       </c>
       <c r="H38" s="2">
-        <v>44561</v>
+        <v>44196</v>
       </c>
       <c r="I38" s="2">
-        <v>44196</v>
+        <v>43830</v>
       </c>
       <c r="J38" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K38" s="2">
         <v>43465</v>
@@ -1656,19 +1656,19 @@
         <v>25344200</v>
       </c>
       <c r="F41" s="3">
-        <v>33470500</v>
+        <v>18602500</v>
       </c>
       <c r="G41" s="3">
-        <v>18602500</v>
+        <v>25724600</v>
       </c>
       <c r="H41" s="3">
-        <v>25724600</v>
+        <v>24188800</v>
       </c>
       <c r="I41" s="3">
-        <v>24188800</v>
+        <v>20774400</v>
       </c>
       <c r="J41" s="3">
-        <v>20774400</v>
+        <v>20068600</v>
       </c>
       <c r="K41" s="3">
         <v>20068600</v>
@@ -1683,25 +1683,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>65640500</v>
+        <v>68153200</v>
       </c>
       <c r="E42" s="3">
-        <v>55265000</v>
+        <v>57943000</v>
       </c>
       <c r="F42" s="3">
-        <v>48228000</v>
+        <v>45177000</v>
       </c>
       <c r="G42" s="3">
-        <v>45177000</v>
+        <v>37953100</v>
       </c>
       <c r="H42" s="3">
-        <v>37953100</v>
+        <v>53040900</v>
       </c>
       <c r="I42" s="3">
-        <v>53040900</v>
+        <v>73195100</v>
       </c>
       <c r="J42" s="3">
-        <v>73195100</v>
+        <v>60588700</v>
       </c>
       <c r="K42" s="3">
         <v>60588700</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4018800</v>
+        <v>1506100</v>
       </c>
       <c r="E43" s="3">
-        <v>4100600</v>
+        <v>1422600</v>
       </c>
       <c r="F43" s="3">
-        <v>3718400</v>
+        <v>2333800</v>
       </c>
       <c r="G43" s="3">
-        <v>2367500</v>
+        <v>2080100</v>
       </c>
       <c r="H43" s="3">
-        <v>2080100</v>
+        <v>2007200</v>
       </c>
       <c r="I43" s="3">
-        <v>2007200</v>
+        <v>3268000</v>
       </c>
       <c r="J43" s="3">
-        <v>3268000</v>
+        <v>3215000</v>
       </c>
       <c r="K43" s="3">
         <v>3215000</v>
@@ -1755,19 +1755,19 @@
         <v>567300</v>
       </c>
       <c r="F44" s="3">
-        <v>641200</v>
+        <v>655300</v>
       </c>
       <c r="G44" s="3">
-        <v>655300</v>
+        <v>746200</v>
       </c>
       <c r="H44" s="3">
-        <v>746200</v>
+        <v>926500</v>
       </c>
       <c r="I44" s="3">
-        <v>926500</v>
+        <v>1416900</v>
       </c>
       <c r="J44" s="3">
-        <v>1416900</v>
+        <v>1534100</v>
       </c>
       <c r="K44" s="3">
         <v>1534100</v>
@@ -1788,19 +1788,19 @@
         <v>12107800</v>
       </c>
       <c r="F45" s="3">
-        <v>11127500</v>
+        <v>10008100</v>
       </c>
       <c r="G45" s="3">
-        <v>10008100</v>
+        <v>8490200</v>
       </c>
       <c r="H45" s="3">
-        <v>8490200</v>
+        <v>7426200</v>
       </c>
       <c r="I45" s="3">
-        <v>7426200</v>
+        <v>7917200</v>
       </c>
       <c r="J45" s="3">
-        <v>7917200</v>
+        <v>5784900</v>
       </c>
       <c r="K45" s="3">
         <v>5784900</v>
@@ -1821,19 +1821,19 @@
         <v>130490900</v>
       </c>
       <c r="F46" s="3">
-        <v>138361300</v>
+        <v>121910200</v>
       </c>
       <c r="G46" s="3">
-        <v>121943800</v>
+        <v>124324400</v>
       </c>
       <c r="H46" s="3">
-        <v>124324400</v>
+        <v>138270400</v>
       </c>
       <c r="I46" s="3">
-        <v>138270400</v>
+        <v>152789200</v>
       </c>
       <c r="J46" s="3">
-        <v>152789200</v>
+        <v>139820000</v>
       </c>
       <c r="K46" s="3">
         <v>139820000</v>
@@ -1854,19 +1854,19 @@
         <v>306941300</v>
       </c>
       <c r="F47" s="3">
-        <v>300988900</v>
+        <v>305952600</v>
       </c>
       <c r="G47" s="3">
-        <v>305952600</v>
+        <v>306737600</v>
       </c>
       <c r="H47" s="3">
-        <v>306737600</v>
+        <v>308672900</v>
       </c>
       <c r="I47" s="3">
-        <v>308672900</v>
+        <v>282084200</v>
       </c>
       <c r="J47" s="3">
-        <v>282084200</v>
+        <v>265387600</v>
       </c>
       <c r="K47" s="3">
         <v>265387600</v>
@@ -1881,25 +1881,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9472400</v>
+        <v>8894400</v>
       </c>
       <c r="E48" s="3">
-        <v>9863500</v>
+        <v>9270200</v>
       </c>
       <c r="F48" s="3">
-        <v>10402500</v>
+        <v>10444100</v>
       </c>
       <c r="G48" s="3">
-        <v>10444100</v>
+        <v>11158600</v>
       </c>
       <c r="H48" s="3">
-        <v>11158600</v>
+        <v>9282200</v>
       </c>
       <c r="I48" s="3">
-        <v>9282200</v>
+        <v>8758700</v>
       </c>
       <c r="J48" s="3">
-        <v>8758700</v>
+        <v>7090000</v>
       </c>
       <c r="K48" s="3">
         <v>7090000</v>
@@ -1914,25 +1914,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>879700</v>
+        <v>1289500</v>
       </c>
       <c r="E49" s="3">
-        <v>709000</v>
+        <v>1129200</v>
       </c>
       <c r="F49" s="3">
-        <v>414300</v>
+        <v>363300</v>
       </c>
       <c r="G49" s="3">
-        <v>363300</v>
+        <v>331400</v>
       </c>
       <c r="H49" s="3">
-        <v>331400</v>
+        <v>785900</v>
       </c>
       <c r="I49" s="3">
-        <v>785900</v>
+        <v>705600</v>
       </c>
       <c r="J49" s="3">
-        <v>705600</v>
+        <v>720700</v>
       </c>
       <c r="K49" s="3">
         <v>720700</v>
@@ -2019,19 +2019,19 @@
         <v>1795600</v>
       </c>
       <c r="F52" s="3">
-        <v>2347100</v>
+        <v>2610000</v>
       </c>
       <c r="G52" s="3">
-        <v>2395600</v>
+        <v>3831300</v>
       </c>
       <c r="H52" s="3">
-        <v>3831300</v>
+        <v>4563800</v>
       </c>
       <c r="I52" s="3">
-        <v>4563800</v>
+        <v>4112700</v>
       </c>
       <c r="J52" s="3">
-        <v>4112700</v>
+        <v>3933700</v>
       </c>
       <c r="K52" s="3">
         <v>3933700</v>
@@ -2085,19 +2085,19 @@
         <v>1070675700</v>
       </c>
       <c r="F54" s="3">
-        <v>1082368200</v>
+        <v>1051973700</v>
       </c>
       <c r="G54" s="3">
-        <v>1051973700</v>
+        <v>1094478800</v>
       </c>
       <c r="H54" s="3">
-        <v>1094478800</v>
+        <v>1064582500</v>
       </c>
       <c r="I54" s="3">
-        <v>1064582500</v>
+        <v>959634800</v>
       </c>
       <c r="J54" s="3">
-        <v>959634800</v>
+        <v>871631800</v>
       </c>
       <c r="K54" s="3">
         <v>871631800</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>750539900</v>
+        <v>736689800</v>
       </c>
       <c r="E57" s="3">
-        <v>728917700</v>
+        <v>717617400</v>
       </c>
       <c r="F57" s="3">
-        <v>778564500</v>
+        <v>793201000</v>
       </c>
       <c r="G57" s="3">
-        <v>792843200</v>
+        <v>797980700</v>
       </c>
       <c r="H57" s="3">
-        <v>797980700</v>
+        <v>710572300</v>
       </c>
       <c r="I57" s="3">
-        <v>710572300</v>
+        <v>664735800</v>
       </c>
       <c r="J57" s="3">
-        <v>664735800</v>
+        <v>617878700</v>
       </c>
       <c r="K57" s="3">
         <v>617878700</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>215749000</v>
+        <v>229650400</v>
       </c>
       <c r="E58" s="3">
-        <v>201203700</v>
+        <v>212556500</v>
       </c>
       <c r="F58" s="3">
-        <v>167787400</v>
+        <v>122249200</v>
       </c>
       <c r="G58" s="3">
-        <v>122249200</v>
+        <v>148930200</v>
       </c>
       <c r="H58" s="3">
-        <v>148930200</v>
+        <v>223248200</v>
       </c>
       <c r="I58" s="3">
-        <v>223248200</v>
+        <v>170120900</v>
       </c>
       <c r="J58" s="3">
-        <v>170120900</v>
+        <v>139583600</v>
       </c>
       <c r="K58" s="3">
         <v>139583600</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1400800</v>
+        <v>1382000</v>
       </c>
       <c r="E59" s="3">
-        <v>1288400</v>
+        <v>1271000</v>
       </c>
       <c r="F59" s="3">
-        <v>875800</v>
+        <v>1449000</v>
       </c>
       <c r="G59" s="3">
-        <v>1749100</v>
+        <v>2182100</v>
       </c>
       <c r="H59" s="3">
-        <v>2182100</v>
+        <v>3689800</v>
       </c>
       <c r="I59" s="3">
-        <v>3689800</v>
+        <v>3530700</v>
       </c>
       <c r="J59" s="3">
-        <v>3530700</v>
+        <v>1856700</v>
       </c>
       <c r="K59" s="3">
         <v>1856700</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>981359400</v>
+        <v>981386400</v>
       </c>
       <c r="E60" s="3">
-        <v>946304700</v>
+        <v>946325300</v>
       </c>
       <c r="F60" s="3">
-        <v>960793100</v>
+        <v>928992500</v>
       </c>
       <c r="G60" s="3">
-        <v>929027600</v>
+        <v>960955400</v>
       </c>
       <c r="H60" s="3">
-        <v>960955400</v>
+        <v>946632800</v>
       </c>
       <c r="I60" s="3">
-        <v>946632800</v>
+        <v>845917500</v>
       </c>
       <c r="J60" s="3">
-        <v>845917500</v>
+        <v>766545400</v>
       </c>
       <c r="K60" s="3">
         <v>766545400</v>
@@ -2280,19 +2280,19 @@
         <v>18741400</v>
       </c>
       <c r="F61" s="3">
-        <v>22310300</v>
+        <v>29171400</v>
       </c>
       <c r="G61" s="3">
-        <v>29171400</v>
+        <v>36520800</v>
       </c>
       <c r="H61" s="3">
-        <v>36520800</v>
+        <v>30693100</v>
       </c>
       <c r="I61" s="3">
-        <v>30693100</v>
+        <v>32803100</v>
       </c>
       <c r="J61" s="3">
-        <v>32803100</v>
+        <v>36576500</v>
       </c>
       <c r="K61" s="3">
         <v>36576500</v>
@@ -2307,25 +2307,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18088300</v>
+        <v>18061300</v>
       </c>
       <c r="E62" s="3">
-        <v>15528100</v>
+        <v>15507500</v>
       </c>
       <c r="F62" s="3">
-        <v>9195000</v>
+        <v>4848600</v>
       </c>
       <c r="G62" s="3">
-        <v>4810600</v>
+        <v>4493900</v>
       </c>
       <c r="H62" s="3">
-        <v>4493900</v>
+        <v>4181800</v>
       </c>
       <c r="I62" s="3">
-        <v>4181800</v>
+        <v>4505700</v>
       </c>
       <c r="J62" s="3">
-        <v>4505700</v>
+        <v>5748000</v>
       </c>
       <c r="K62" s="3">
         <v>5748000</v>
@@ -2445,19 +2445,19 @@
         <v>980723800</v>
       </c>
       <c r="F66" s="3">
-        <v>992421800</v>
+        <v>963124000</v>
       </c>
       <c r="G66" s="3">
-        <v>963124000</v>
+        <v>1002148300</v>
       </c>
       <c r="H66" s="3">
-        <v>1002148300</v>
+        <v>981678300</v>
       </c>
       <c r="I66" s="3">
-        <v>981678300</v>
+        <v>883398000</v>
       </c>
       <c r="J66" s="3">
-        <v>883398000</v>
+        <v>808965400</v>
       </c>
       <c r="K66" s="3">
         <v>808965400</v>
@@ -2559,19 +2559,19 @@
         <v>2740100</v>
       </c>
       <c r="F70" s="3">
-        <v>2820500</v>
+        <v>2896100</v>
       </c>
       <c r="G70" s="3">
-        <v>2896100</v>
+        <v>3144400</v>
       </c>
       <c r="H70" s="3">
-        <v>3144400</v>
+        <v>4574800</v>
       </c>
       <c r="I70" s="3">
-        <v>4574800</v>
+        <v>4289400</v>
       </c>
       <c r="J70" s="3">
-        <v>4289400</v>
+        <v>1438300</v>
       </c>
       <c r="K70" s="3">
         <v>1438300</v>
@@ -2625,19 +2625,19 @@
         <v>60116700</v>
       </c>
       <c r="F72" s="3">
-        <v>60032900</v>
+        <v>58523300</v>
       </c>
       <c r="G72" s="3">
-        <v>58523300</v>
+        <v>60132900</v>
       </c>
       <c r="H72" s="3">
-        <v>60132900</v>
+        <v>55191800</v>
       </c>
       <c r="I72" s="3">
-        <v>55191800</v>
+        <v>49629500</v>
       </c>
       <c r="J72" s="3">
-        <v>49629500</v>
+        <v>44696900</v>
       </c>
       <c r="K72" s="3">
         <v>44696900</v>
@@ -2757,19 +2757,19 @@
         <v>85333700</v>
       </c>
       <c r="F76" s="3">
-        <v>85264500</v>
+        <v>84085300</v>
       </c>
       <c r="G76" s="3">
-        <v>84085300</v>
+        <v>87256400</v>
       </c>
       <c r="H76" s="3">
-        <v>87256400</v>
+        <v>76535600</v>
       </c>
       <c r="I76" s="3">
-        <v>76535600</v>
+        <v>70226200</v>
       </c>
       <c r="J76" s="3">
-        <v>70226200</v>
+        <v>59639400</v>
       </c>
       <c r="K76" s="3">
         <v>59639400</v>
@@ -2828,19 +2828,19 @@
         <v>45657</v>
       </c>
       <c r="F80" s="2">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G80" s="2">
-        <v>44926</v>
+        <v>44561</v>
       </c>
       <c r="H80" s="2">
-        <v>44561</v>
+        <v>44196</v>
       </c>
       <c r="I80" s="2">
-        <v>44196</v>
+        <v>43830</v>
       </c>
       <c r="J80" s="2">
-        <v>43830</v>
+        <v>43465</v>
       </c>
       <c r="K80" s="2">
         <v>43465</v>
@@ -2861,19 +2861,19 @@
         <v>4424700</v>
       </c>
       <c r="F81" s="3">
-        <v>5052000</v>
+        <v>5113500</v>
       </c>
       <c r="G81" s="3">
-        <v>5113500</v>
+        <v>5412100</v>
       </c>
       <c r="H81" s="3">
-        <v>5412100</v>
+        <v>5255200</v>
       </c>
       <c r="I81" s="3">
-        <v>5255200</v>
+        <v>7729400</v>
       </c>
       <c r="J81" s="3">
-        <v>7729400</v>
+        <v>7317400</v>
       </c>
       <c r="K81" s="3">
         <v>7317400</v>
@@ -2903,25 +2903,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>991900</v>
+        <v>974200</v>
       </c>
       <c r="E83" s="3">
-        <v>1015200</v>
+        <v>1000100</v>
       </c>
       <c r="F83" s="3">
-        <v>1044400</v>
+        <v>1023300</v>
       </c>
       <c r="G83" s="3">
-        <v>1023300</v>
+        <v>1067600</v>
       </c>
       <c r="H83" s="3">
-        <v>1067600</v>
+        <v>1061800</v>
       </c>
       <c r="I83" s="3">
-        <v>1061800</v>
+        <v>840200</v>
       </c>
       <c r="J83" s="3">
-        <v>840200</v>
+        <v>979300</v>
       </c>
       <c r="K83" s="3">
         <v>979300</v>
@@ -3101,25 +3101,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-10111100</v>
+        <v>-22514600</v>
       </c>
       <c r="E89" s="3">
-        <v>-4277500</v>
+        <v>-31735100</v>
       </c>
       <c r="F89" s="3">
-        <v>3000700</v>
+        <v>-34372200</v>
       </c>
       <c r="G89" s="3">
-        <v>-34372200</v>
+        <v>-17921200</v>
       </c>
       <c r="H89" s="3">
-        <v>-17921200</v>
+        <v>-12621700</v>
       </c>
       <c r="I89" s="3">
-        <v>-12621700</v>
+        <v>-12197100</v>
       </c>
       <c r="J89" s="3">
-        <v>-12197100</v>
+        <v>-53136100</v>
       </c>
       <c r="K89" s="3">
         <v>-53136100</v>
@@ -3155,19 +3155,19 @@
         <v>-1329900</v>
       </c>
       <c r="F91" s="3">
-        <v>-1223700</v>
+        <v>-1553100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1553100</v>
+        <v>-1489900</v>
       </c>
       <c r="H91" s="3">
-        <v>-1489900</v>
+        <v>-1196900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1196900</v>
+        <v>-1180300</v>
       </c>
       <c r="J91" s="3">
-        <v>-1180300</v>
+        <v>-843700</v>
       </c>
       <c r="K91" s="3">
         <v>-843700</v>
@@ -3254,19 +3254,19 @@
         <v>-5866600</v>
       </c>
       <c r="F94" s="3">
-        <v>5889800</v>
+        <v>-16285900</v>
       </c>
       <c r="G94" s="3">
-        <v>-16285900</v>
+        <v>18560600</v>
       </c>
       <c r="H94" s="3">
-        <v>18560600</v>
+        <v>1173300</v>
       </c>
       <c r="I94" s="3">
-        <v>1173300</v>
+        <v>-9635500</v>
       </c>
       <c r="J94" s="3">
-        <v>-9635500</v>
+        <v>40934000</v>
       </c>
       <c r="K94" s="3">
         <v>40934000</v>
@@ -3302,19 +3302,19 @@
         <v>471300</v>
       </c>
       <c r="F96" s="3">
-        <v>485100</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>468300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>297200</v>
       </c>
       <c r="I96" s="3">
-        <v>297200</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>477500</v>
       </c>
       <c r="K96" s="3">
         <v>477500</v>
@@ -3428,25 +3428,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2906900</v>
+        <v>9496600</v>
       </c>
       <c r="E100" s="3">
-        <v>2937900</v>
+        <v>30395500</v>
       </c>
       <c r="F100" s="3">
-        <v>6365600</v>
+        <v>44531100</v>
       </c>
       <c r="G100" s="3">
-        <v>44531100</v>
+        <v>400300</v>
       </c>
       <c r="H100" s="3">
-        <v>400300</v>
+        <v>14086500</v>
       </c>
       <c r="I100" s="3">
-        <v>14086500</v>
+        <v>22646900</v>
       </c>
       <c r="J100" s="3">
-        <v>22646900</v>
+        <v>16204400</v>
       </c>
       <c r="K100" s="3">
         <v>16204400</v>
@@ -3467,19 +3467,19 @@
         <v>34700</v>
       </c>
       <c r="F101" s="3">
-        <v>120000</v>
+        <v>1036100</v>
       </c>
       <c r="G101" s="3">
-        <v>1036100</v>
+        <v>-174100</v>
       </c>
       <c r="H101" s="3">
-        <v>-174100</v>
+        <v>-605600</v>
       </c>
       <c r="I101" s="3">
-        <v>-605600</v>
+        <v>137000</v>
       </c>
       <c r="J101" s="3">
-        <v>137000</v>
+        <v>203600</v>
       </c>
       <c r="K101" s="3">
         <v>203600</v>
@@ -3500,19 +3500,19 @@
         <v>-7171600</v>
       </c>
       <c r="F102" s="3">
-        <v>15376200</v>
+        <v>-5090900</v>
       </c>
       <c r="G102" s="3">
-        <v>-5090900</v>
+        <v>865600</v>
       </c>
       <c r="H102" s="3">
-        <v>865600</v>
+        <v>2032400</v>
       </c>
       <c r="I102" s="3">
-        <v>2032400</v>
+        <v>951300</v>
       </c>
       <c r="J102" s="3">
-        <v>951300</v>
+        <v>4205900</v>
       </c>
       <c r="K102" s="3">
         <v>4205900</v>
